--- a/resources/reselling/files/reselling-basics-real-net-calculator.xlsx
+++ b/resources/reselling/files/reselling-basics-real-net-calculator.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,9 +139,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -513,13 +510,13 @@
   <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="51" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="3" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Real-net &amp; max-buy calculator — the deal sheet (Basics, ch4-6)</t>
         </is>
@@ -685,9 +682,9 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
